--- a/output/roomself_excel/13185.xlsx
+++ b/output/roomself_excel/13185.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>385319</v>
+        <v>114179</v>
       </c>
       <c r="D2" t="n">
-        <v>7619</v>
+        <v>2724</v>
       </c>
       <c r="E2" t="n">
-        <v>966</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>58202</v>
+        <v>202109</v>
       </c>
       <c r="D3" t="n">
-        <v>2116</v>
+        <v>3756</v>
       </c>
       <c r="E3" t="n">
-        <v>614</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35150</v>
+        <v>113212</v>
       </c>
       <c r="D4" t="n">
-        <v>1500</v>
+        <v>2692</v>
       </c>
       <c r="E4" t="n">
-        <v>216</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30212</v>
+        <v>109434</v>
       </c>
       <c r="D5" t="n">
-        <v>1392</v>
+        <v>2656</v>
       </c>
       <c r="E5" t="n">
-        <v>166</v>
+        <v>303</v>
       </c>
       <c r="F5" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>113212</v>
+        <v>58202</v>
       </c>
       <c r="D6" t="n">
-        <v>2692</v>
+        <v>2116</v>
       </c>
       <c r="E6" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>109434</v>
+        <v>35150</v>
       </c>
       <c r="D7" t="n">
-        <v>2656</v>
+        <v>1500</v>
       </c>
       <c r="E7" t="n">
-        <v>387</v>
+        <v>185</v>
       </c>
       <c r="F7" t="n">
-        <v>336</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15369</v>
+        <v>16356</v>
       </c>
       <c r="D8" t="n">
-        <v>1000</v>
+        <v>1028</v>
       </c>
       <c r="E8" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16356</v>
+        <v>68774</v>
       </c>
       <c r="D9" t="n">
-        <v>1028</v>
+        <v>3480</v>
       </c>
       <c r="E9" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,86 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Hallway</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>15369</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Storage</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C11" t="n">
         <v>15651</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" t="n">
         <v>1008</v>
       </c>
-      <c r="E10" t="n">
-        <v>111</v>
-      </c>
-      <c r="F10" t="n">
-        <v>32</v>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>30212</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1392</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>257</v>
+      </c>
+      <c r="D13" t="n">
+        <v>279</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/13185.xlsx
+++ b/output/roomself_excel/13185.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,17 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
         </is>
       </c>
     </row>
@@ -475,12 +480,9 @@
       <c r="D2" t="n">
         <v>2724</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +499,9 @@
       <c r="D3" t="n">
         <v>3756</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +518,9 @@
       <c r="D4" t="n">
         <v>2692</v>
       </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,10 +537,15 @@
       <c r="D5" t="n">
         <v>2656</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>303</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>27</v>
       </c>
     </row>
@@ -563,12 +564,9 @@
       <c r="D6" t="n">
         <v>2116</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,10 +583,15 @@
       <c r="D7" t="n">
         <v>1500</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>185</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>26</v>
       </c>
     </row>
@@ -607,12 +610,9 @@
       <c r="D8" t="n">
         <v>1028</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +629,9 @@
       <c r="D9" t="n">
         <v>3480</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +648,9 @@
       <c r="D10" t="n">
         <v>1000</v>
       </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +667,9 @@
       <c r="D11" t="n">
         <v>1008</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +686,9 @@
       <c r="D12" t="n">
         <v>1392</v>
       </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +705,9 @@
       <c r="D13" t="n">
         <v>279</v>
       </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/13185.xlsx
+++ b/output/roomself_excel/13185.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
